--- a/sources/fundamentals.xlsx
+++ b/sources/fundamentals.xlsx
@@ -416,7 +416,7 @@
   <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="15.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="11.92"/>
